--- a/CENSOS-BOVINOS-2025-Final.xlsx
+++ b/CENSOS-BOVINOS-2025-Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atolosa\Desktop\Python\DatosBovinos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atolosa\Downloads\AGT\Python\DatosBovinos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5892B143-D2EF-47A3-9C64-A559004092E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4195E9-95F0-4856-B520-AC5698361A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOVINOS Y PREDIOS" sheetId="1" r:id="rId1"/>
@@ -6702,7 +6702,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6774,6 +6774,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -6894,7 +6902,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6977,18 +6985,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -8245,7 +8252,7 @@
       <c r="A16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="36" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="18" t="s">
@@ -8465,7 +8472,7 @@
       <c r="A20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -71285,7 +71292,7 @@
   </sheetData>
   <autoFilter ref="A5:O5" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="K5:O5">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(K5))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73036,7 +73043,7 @@
     <mergeCell ref="A1:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="K8:P8">
-    <cfRule type="containsBlanks" dxfId="2" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(K8))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73046,26 +73053,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e8e22fe-4198-4c93-872a-6b6dec0a4266">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d7f80cf4-2863-421f-9003-5cd9b982edd2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006FEDA3CB8E94804F806D323B6854C007" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="89b85a4753469b044cdf8baab9263b63">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e8e22fe-4198-4c93-872a-6b6dec0a4266" xmlns:ns3="d7f80cf4-2863-421f-9003-5cd9b982edd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a389710935737584a49c43d816f81feb" ns2:_="" ns3:_="">
     <xsd:import namespace="8e8e22fe-4198-4c93-872a-6b6dec0a4266"/>
@@ -73282,32 +73269,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B0EB77-956C-4F35-BAA9-7145CF9AC5EA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="d7f80cf4-2863-421f-9003-5cd9b982edd2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e8e22fe-4198-4c93-872a-6b6dec0a4266"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C3F93F-2FE6-49C7-8050-EE8BEDECE07B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e8e22fe-4198-4c93-872a-6b6dec0a4266">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d7f80cf4-2863-421f-9003-5cd9b982edd2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{390D9E8C-70B2-4C19-BA00-38A7F31B5D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -73324,4 +73306,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C3F93F-2FE6-49C7-8050-EE8BEDECE07B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B0EB77-956C-4F35-BAA9-7145CF9AC5EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="d7f80cf4-2863-421f-9003-5cd9b982edd2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e8e22fe-4198-4c93-872a-6b6dec0a4266"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>